--- a/artfynd/A 38194-2026 artfynd.xlsx
+++ b/artfynd/A 38194-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136799079</v>
       </c>
       <c r="B2" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>136797771</v>
       </c>
       <c r="B5" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>136797886</v>
       </c>
       <c r="B6" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>136799406</v>
       </c>
       <c r="B7" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>136798088</v>
       </c>
       <c r="B8" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>136798131</v>
       </c>
       <c r="B9" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>136798480</v>
       </c>
       <c r="B10" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>136799383</v>
       </c>
       <c r="B11" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>136799527</v>
       </c>
       <c r="B12" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>136799553</v>
       </c>
       <c r="B13" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>136799610</v>
       </c>
       <c r="B14" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>136798123</v>
       </c>
       <c r="B15" t="n">
-        <v>93421</v>
+        <v>93423</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>136798750</v>
       </c>
       <c r="B16" t="n">
-        <v>92132</v>
+        <v>92134</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>136798951</v>
       </c>
       <c r="B17" t="n">
-        <v>92132</v>
+        <v>92134</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>136798811</v>
       </c>
       <c r="B18" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>136798059</v>
       </c>
       <c r="B19" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         <v>136798446</v>
       </c>
       <c r="B20" t="n">
-        <v>90893</v>
+        <v>90895</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
